--- a/items.xlsx
+++ b/items.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32FFB16-7C99-48AA-A931-378A738D1E27}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBA90A5-D10A-4F1F-AB77-221C92C5E19B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="아이템" sheetId="1" r:id="rId1"/>
     <sheet name="사용법" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="0" iterate="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="196">
   <si>
     <t>키
 (코드에서 사용)</t>
@@ -137,18 +137,18 @@
     <t>강화 포인트 +100</t>
   </si>
   <si>
+    <t>지옥의불꽃_150</t>
+  </si>
+  <si>
+    <t>🌠 지옥의 불꽃</t>
+  </si>
+  <si>
+    <t>강화 포인트 +150</t>
+  </si>
+  <si>
     <t>완전초기화구슬</t>
   </si>
   <si>
-    <t>지옥의불꽃_150</t>
-  </si>
-  <si>
-    <t>🌠 지옥의 불꽃</t>
-  </si>
-  <si>
-    <t>강화 포인트 +150</t>
-  </si>
-  <si>
     <t>불지옥의불꽃_400</t>
   </si>
   <si>
@@ -299,6 +299,15 @@
     <t>원하는 펫으로 1렙 재생성 (환수 보정·S베이스 유지)</t>
   </si>
   <si>
+    <t>샤르체류알</t>
+  </si>
+  <si>
+    <t>pet_egg_select</t>
+  </si>
+  <si>
+    <t>사용 시 샤르체류 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
+  </si>
+  <si>
     <t>오형제(진화)알</t>
   </si>
   <si>
@@ -326,6 +335,24 @@
     <t>사용 시 쿵야펫 중 1마리로 교체 (환수 보정 유지)</t>
   </si>
   <si>
+    <t>카오닉스알</t>
+  </si>
+  <si>
+    <t>사용 시 카오닉스SD 교체 (환수 보정 유지)</t>
+  </si>
+  <si>
+    <t>언딘알</t>
+  </si>
+  <si>
+    <t>사용 시 언딘 교체 (환수 보정 유지)</t>
+  </si>
+  <si>
+    <t>공룡알</t>
+  </si>
+  <si>
+    <t>사용 시 공룡4종 1마리 랜덤 교체 (환수 보정 유지)</t>
+  </si>
+  <si>
     <t>운영진</t>
   </si>
   <si>
@@ -482,6 +509,9 @@
     <t>awakening</t>
   </si>
   <si>
+    <t>버프,서포터펫에사용 한계치강화</t>
+  </si>
+  <si>
     <t>배진3강화제</t>
   </si>
   <si>
@@ -491,6 +521,9 @@
     <t>awakening_cc3</t>
   </si>
   <si>
+    <t>딜러펫 배진3 5%확률로 업그레이드</t>
+  </si>
+  <si>
     <t>[아이템 엑셀 사용법]</t>
   </si>
   <si>
@@ -585,38 +618,6 @@
   </si>
   <si>
     <t>✅ 교환/판매 O↔X, 판매보상 수치는 자유롭게 수정 가능</t>
-  </si>
-  <si>
-    <t>버프,서포터펫에사용 한계치강화</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>딜러펫 배진3 5%확률로 업그레이드</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>카오닉스알</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용 시 카오닉스SD 교체 (환수 보정 유지)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>언딘알</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용 시 언딘 교체 (환수 보정 유지)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>공룡알</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용 시 공룡4종 1마리 랜덤 교체 (환수 보정 유지)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1067,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1265,10 +1266,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>22</v>
@@ -1277,7 +1278,7 @@
         <v>150</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>24</v>
@@ -1287,7 +1288,7 @@
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J7" s="4">
         <v>3</v>
@@ -1317,7 +1318,7 @@
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J8" s="4">
         <v>10</v>
@@ -1655,7 +1656,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>82</v>
@@ -1714,16 +1715,16 @@
         <v>89</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>62</v>
@@ -1735,7 +1736,7 @@
         <v>500</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J23" s="4">
         <v>5</v>
@@ -1743,13 +1744,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
@@ -1764,10 +1765,10 @@
         <v>24</v>
       </c>
       <c r="H24" s="4">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J24" s="4">
         <v>5</v>
@@ -1778,44 +1779,48 @@
         <v>96</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D25" s="4">
         <v>1</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>24</v>
+        <v>98</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="4">
-        <v>10</v>
-      </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="4"/>
+        <v>700</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J25" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>187</v>
+        <v>99</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>187</v>
+        <v>99</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>24</v>
@@ -1831,19 +1836,19 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>24</v>
@@ -1859,19 +1864,19 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>191</v>
+        <v>103</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>191</v>
+        <v>103</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D28" s="4">
         <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>24</v>
@@ -1887,79 +1892,79 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D29" s="4">
         <v>1</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>62</v>
+        <v>106</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="4">
-        <v>500</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="4">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I29" s="10"/>
+      <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D30" s="4">
         <v>1</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>24</v>
+        <v>107</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="4">
-        <v>10</v>
-      </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="4"/>
+        <v>500</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D31" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>24</v>
@@ -1975,19 +1980,19 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D32" s="4">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>24</v>
@@ -1995,29 +2000,27 @@
       <c r="G32" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J32" s="4">
-        <v>1</v>
-      </c>
+      <c r="H32" s="4">
+        <v>10</v>
+      </c>
+      <c r="I32" s="10"/>
+      <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D33" s="4">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>24</v>
@@ -2030,24 +2033,24 @@
         <v>28</v>
       </c>
       <c r="J33" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D34" s="4">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>24</v>
@@ -2060,24 +2063,24 @@
         <v>28</v>
       </c>
       <c r="J34" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="D35" s="4">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>24</v>
@@ -2087,27 +2090,27 @@
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="10" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J35" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D36" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>24</v>
@@ -2117,7 +2120,7 @@
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="10" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="J36" s="4">
         <v>1</v>
@@ -2125,47 +2128,49 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D37" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J37" s="4">
         <v>1</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="4">
-        <v>10</v>
-      </c>
-      <c r="I37" s="10"/>
-      <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D38" s="4">
         <v>1</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>62</v>
@@ -2181,19 +2186,19 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D39" s="4">
         <v>1</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>62</v>
@@ -2209,19 +2214,19 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D40" s="4">
         <v>1</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>62</v>
@@ -2237,45 +2242,47 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D41" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H41" s="4"/>
+      <c r="G41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="4">
+        <v>10</v>
+      </c>
       <c r="I41" s="10"/>
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D42" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>24</v>
@@ -2289,19 +2296,19 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D43" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>24</v>
@@ -2315,47 +2322,45 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D44" s="10">
-        <v>1</v>
+        <v>154</v>
+      </c>
+      <c r="D44" s="4">
+        <v>5</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H44" s="10">
-        <v>10</v>
-      </c>
+      <c r="G44" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H44" s="4"/>
       <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
+      <c r="J44" s="4"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D45" s="10">
         <v>1</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>24</v>
@@ -2370,9 +2375,37 @@
       <c r="J45" s="10"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
+      <c r="A46" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D46" s="10">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="10">
+        <v>10</v>
+      </c>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -2392,99 +2425,99 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -2492,15 +2525,15 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2508,32 +2541,32 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/items.xlsx
+++ b/items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBA90A5-D10A-4F1F-AB77-221C92C5E19B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9637BB9-E4E1-44F4-9431-675B1FD579FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="아이템" sheetId="1" r:id="rId1"/>
     <sheet name="사용법" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterate="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="199">
   <si>
     <t>키
 (코드에서 사용)</t>
@@ -314,24 +314,24 @@
     <t>🥚 오형제(진화)알</t>
   </si>
   <si>
+    <t>사용 시 오형제 진화 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
+  </si>
+  <si>
+    <t>천상펫알</t>
+  </si>
+  <si>
+    <t>🥚 천상펫알</t>
+  </si>
+  <si>
+    <t>사용 시 고오다,아마란 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
+  </si>
+  <si>
+    <t>쿵야알</t>
+  </si>
+  <si>
     <t>pet_egg</t>
   </si>
   <si>
-    <t>사용 시 오형제 진화 펫 중 1마리로 교체 (환수 보정 유지)</t>
-  </si>
-  <si>
-    <t>천상펫알</t>
-  </si>
-  <si>
-    <t>🥚 천상펫알</t>
-  </si>
-  <si>
-    <t>사용 시 고오다,아마란 펫 중 1마리로 교체 (환수 보정 유지)</t>
-  </si>
-  <si>
-    <t>쿵야알</t>
-  </si>
-  <si>
     <t>사용 시 쿵야펫 중 1마리로 교체 (환수 보정 유지)</t>
   </si>
   <si>
@@ -407,224 +407,257 @@
     <t>펫 경험치 +700</t>
   </si>
   <si>
+    <t>📜 펫 경험의 문서 (+1000)</t>
+  </si>
+  <si>
+    <t>펫 경험치 +1000</t>
+  </si>
+  <si>
+    <t>펫경문_2000</t>
+  </si>
+  <si>
+    <t>📜 펫 경험의 문서 (+2000)</t>
+  </si>
+  <si>
+    <t>펫 경험치 +2000</t>
+  </si>
+  <si>
+    <t>사냥상자_하급</t>
+  </si>
+  <si>
+    <t>📦 하급 상자</t>
+  </si>
+  <si>
+    <t>hunt_chest_common</t>
+  </si>
+  <si>
+    <t>사냥 중 획득한 상자 (열면 아이템 1개 랜덤 지급)</t>
+  </si>
+  <si>
+    <t>사냥상자_중급</t>
+  </si>
+  <si>
+    <t>🎁 중급 상자</t>
+  </si>
+  <si>
+    <t>hunt_chest_rare</t>
+  </si>
+  <si>
+    <t>사냥상자_상급</t>
+  </si>
+  <si>
+    <t>💜 상급 상자</t>
+  </si>
+  <si>
+    <t>hunt_chest_epic</t>
+  </si>
+  <si>
+    <t>사냥상자_최상급</t>
+  </si>
+  <si>
+    <t>🌟 최상급 상자</t>
+  </si>
+  <si>
+    <t>hunt_chest_legendary</t>
+  </si>
+  <si>
+    <t>초기화꾸러미</t>
+  </si>
+  <si>
+    <t>🎁 초기화꾸러미</t>
+  </si>
+  <si>
+    <t>bundle_reset_orb</t>
+  </si>
+  <si>
+    <t>사용 시 초기화구슬 20개 획득</t>
+  </si>
+  <si>
+    <t>완전초기화꾸러미</t>
+  </si>
+  <si>
+    <t>🎀 완전초기화꾸러미</t>
+  </si>
+  <si>
+    <t>bundle_full_reset_orb</t>
+  </si>
+  <si>
+    <t>사용 시 완전초기화구슬 10개 획득</t>
+  </si>
+  <si>
+    <t>지정초기화꾸러미</t>
+  </si>
+  <si>
+    <t>🎀 지정초기화꾸러미</t>
+  </si>
+  <si>
+    <t>bundle_designated_reset_orb</t>
+  </si>
+  <si>
+    <t>사용 시 지정초기화구슬 5개 획득</t>
+  </si>
+  <si>
+    <t>각성제</t>
+  </si>
+  <si>
+    <t>💊 각성제</t>
+  </si>
+  <si>
+    <t>awakening</t>
+  </si>
+  <si>
+    <t>버프,서포터펫에사용 한계치강화</t>
+  </si>
+  <si>
+    <t>☠️ 배진3 강화제</t>
+  </si>
+  <si>
+    <t>awakening_cc3</t>
+  </si>
+  <si>
+    <t>딜러펫 배진3 5%확률로 업그레이드</t>
+  </si>
+  <si>
+    <t>[아이템 엑셀 사용법]</t>
+  </si>
+  <si>
+    <t>1. '아이템' 시트에서 아이템을 추가/수정/삭제합니다.</t>
+  </si>
+  <si>
+    <t>2. 봇 시작 시 자동으로 이 엑셀을 읽어서 아이템 데이터를 구성합니다.</t>
+  </si>
+  <si>
+    <t>3. 봇 실행 중에 !아이템리로드 명령어로 즉시 반영 가능합니다.</t>
+  </si>
+  <si>
+    <t>[컬럼 설명]</t>
+  </si>
+  <si>
+    <t>키 (key)</t>
+  </si>
+  <si>
+    <t>코드에서 사용하는 고유 식별자. 변경 시 raid.py, pet.py 보상풀 연동 깨짐</t>
+  </si>
+  <si>
+    <t>이모지+이름 (name)</t>
+  </si>
+  <si>
+    <t>인벤토리에 표시되는 이름. ⚠ 변경 시 기존 유저 인벤토리 매칭 안 됨!</t>
+  </si>
+  <si>
+    <t>타입 (type)</t>
+  </si>
+  <si>
+    <t>enhance_points, enhance_x2, raid_tokens, stat_points, pet_reset, pet_full_reset, pet_egg, pet_exp, hunt_chest_* 등</t>
+  </si>
+  <si>
+    <t>값 (value)</t>
+  </si>
+  <si>
+    <t>효과 수치 (강화포인트 양, 배율 등)</t>
+  </si>
+  <si>
+    <t>설명 (desc)</t>
+  </si>
+  <si>
+    <t>인벤토리에 표시되는 설명문</t>
+  </si>
+  <si>
+    <t>교환 (tradeable)</t>
+  </si>
+  <si>
+    <t>O = !교환 목록에 표시, X = 교환 불가 (드롭다운에서 숨김)</t>
+  </si>
+  <si>
+    <t>판매 (sellable)</t>
+  </si>
+  <si>
+    <t>O = !판매 목록에 표시, X = 판매 불가 (드롭다운에서 숨김)</t>
+  </si>
+  <si>
+    <t>판매보상_포인트</t>
+  </si>
+  <si>
+    <t>판매 시 1개당 지급할 강화포인트 (비워두면 0)</t>
+  </si>
+  <si>
+    <t>판매보상_아이템키</t>
+  </si>
+  <si>
+    <t>판매 시 지급할 아이템의 '키' (예: 초기화구슬, 소환권상자_5). 비워두면 미지급</t>
+  </si>
+  <si>
+    <t>위 아이템 1개 판매당 지급 갯수</t>
+  </si>
+  <si>
+    <t>소스 (source)</t>
+  </si>
+  <si>
+    <t>알 아이템 전용. pet_stats.xlsx의 source 열과 매칭해서 펫 후보 필터링</t>
+  </si>
+  <si>
+    <t>[주의사항]</t>
+  </si>
+  <si>
+    <t>⚠ 'name' 변경 → 기존 유저 보유 아이템 매칭 안 됨</t>
+  </si>
+  <si>
+    <t>⚠ 'key' 변경 → raid.py, pet.py 보상 풀 연동 깨짐</t>
+  </si>
+  <si>
+    <t>⚠ 2행(영문 키 행) 절대 수정 금지</t>
+  </si>
+  <si>
+    <t>✅ 새 아이템 추가는 자유롭게 가능</t>
+  </si>
+  <si>
+    <t>✅ 교환/판매 O↔X, 판매보상 수치는 자유롭게 수정 가능</t>
+  </si>
+  <si>
     <t>펫경문_1000</t>
-  </si>
-  <si>
-    <t>📜 펫 경험의 문서 (+1000)</t>
-  </si>
-  <si>
-    <t>펫 경험치 +1000</t>
-  </si>
-  <si>
-    <t>펫경문_2000</t>
-  </si>
-  <si>
-    <t>📜 펫 경험의 문서 (+2000)</t>
-  </si>
-  <si>
-    <t>펫 경험치 +2000</t>
-  </si>
-  <si>
-    <t>사냥상자_하급</t>
-  </si>
-  <si>
-    <t>📦 하급 상자</t>
-  </si>
-  <si>
-    <t>hunt_chest_common</t>
-  </si>
-  <si>
-    <t>사냥 중 획득한 상자 (열면 아이템 1개 랜덤 지급)</t>
-  </si>
-  <si>
-    <t>사냥상자_중급</t>
-  </si>
-  <si>
-    <t>🎁 중급 상자</t>
-  </si>
-  <si>
-    <t>hunt_chest_rare</t>
-  </si>
-  <si>
-    <t>사냥상자_상급</t>
-  </si>
-  <si>
-    <t>💜 상급 상자</t>
-  </si>
-  <si>
-    <t>hunt_chest_epic</t>
-  </si>
-  <si>
-    <t>사냥상자_최상급</t>
-  </si>
-  <si>
-    <t>🌟 최상급 상자</t>
-  </si>
-  <si>
-    <t>hunt_chest_legendary</t>
-  </si>
-  <si>
-    <t>초기화꾸러미</t>
-  </si>
-  <si>
-    <t>🎁 초기화꾸러미</t>
-  </si>
-  <si>
-    <t>bundle_reset_orb</t>
-  </si>
-  <si>
-    <t>사용 시 초기화구슬 20개 획득</t>
-  </si>
-  <si>
-    <t>완전초기화꾸러미</t>
-  </si>
-  <si>
-    <t>🎀 완전초기화꾸러미</t>
-  </si>
-  <si>
-    <t>bundle_full_reset_orb</t>
-  </si>
-  <si>
-    <t>사용 시 완전초기화구슬 10개 획득</t>
-  </si>
-  <si>
-    <t>지정초기화꾸러미</t>
-  </si>
-  <si>
-    <t>🎀 지정초기화꾸러미</t>
-  </si>
-  <si>
-    <t>bundle_designated_reset_orb</t>
-  </si>
-  <si>
-    <t>사용 시 지정초기화구슬 5개 획득</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>배진3강화제</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>펫경문_3000</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 펫 경험의 문서 (+3000)</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>각성제</t>
-  </si>
-  <si>
-    <t>💊 각성제</t>
-  </si>
-  <si>
-    <t>awakening</t>
-  </si>
-  <si>
-    <t>버프,서포터펫에사용 한계치강화</t>
-  </si>
-  <si>
-    <t>배진3강화제</t>
-  </si>
-  <si>
-    <t>☠️ 배진3 강화제</t>
-  </si>
-  <si>
-    <t>awakening_cc3</t>
-  </si>
-  <si>
-    <t>딜러펫 배진3 5%확률로 업그레이드</t>
-  </si>
-  <si>
-    <t>[아이템 엑셀 사용법]</t>
-  </si>
-  <si>
-    <t>1. '아이템' 시트에서 아이템을 추가/수정/삭제합니다.</t>
-  </si>
-  <si>
-    <t>2. 봇 시작 시 자동으로 이 엑셀을 읽어서 아이템 데이터를 구성합니다.</t>
-  </si>
-  <si>
-    <t>3. 봇 실행 중에 !아이템리로드 명령어로 즉시 반영 가능합니다.</t>
-  </si>
-  <si>
-    <t>[컬럼 설명]</t>
-  </si>
-  <si>
-    <t>키 (key)</t>
-  </si>
-  <si>
-    <t>코드에서 사용하는 고유 식별자. 변경 시 raid.py, pet.py 보상풀 연동 깨짐</t>
-  </si>
-  <si>
-    <t>이모지+이름 (name)</t>
-  </si>
-  <si>
-    <t>인벤토리에 표시되는 이름. ⚠ 변경 시 기존 유저 인벤토리 매칭 안 됨!</t>
-  </si>
-  <si>
-    <t>타입 (type)</t>
-  </si>
-  <si>
-    <t>enhance_points, enhance_x2, raid_tokens, stat_points, pet_reset, pet_full_reset, pet_egg, pet_exp, hunt_chest_* 등</t>
-  </si>
-  <si>
-    <t>값 (value)</t>
-  </si>
-  <si>
-    <t>효과 수치 (강화포인트 양, 배율 등)</t>
-  </si>
-  <si>
-    <t>설명 (desc)</t>
-  </si>
-  <si>
-    <t>인벤토리에 표시되는 설명문</t>
-  </si>
-  <si>
-    <t>교환 (tradeable)</t>
-  </si>
-  <si>
-    <t>O = !교환 목록에 표시, X = 교환 불가 (드롭다운에서 숨김)</t>
-  </si>
-  <si>
-    <t>판매 (sellable)</t>
-  </si>
-  <si>
-    <t>O = !판매 목록에 표시, X = 판매 불가 (드롭다운에서 숨김)</t>
-  </si>
-  <si>
-    <t>판매보상_포인트</t>
-  </si>
-  <si>
-    <t>판매 시 1개당 지급할 강화포인트 (비워두면 0)</t>
-  </si>
-  <si>
-    <t>판매보상_아이템키</t>
-  </si>
-  <si>
-    <t>판매 시 지급할 아이템의 '키' (예: 초기화구슬, 소환권상자_5). 비워두면 미지급</t>
-  </si>
-  <si>
-    <t>위 아이템 1개 판매당 지급 갯수</t>
-  </si>
-  <si>
-    <t>소스 (source)</t>
-  </si>
-  <si>
-    <t>알 아이템 전용. pet_stats.xlsx의 source 열과 매칭해서 펫 후보 필터링</t>
-  </si>
-  <si>
-    <t>[주의사항]</t>
-  </si>
-  <si>
-    <t>⚠ 'name' 변경 → 기존 유저 보유 아이템 매칭 안 됨</t>
-  </si>
-  <si>
-    <t>⚠ 'key' 변경 → raid.py, pet.py 보상 풀 연동 깨짐</t>
-  </si>
-  <si>
-    <t>⚠ 2행(영문 키 행) 절대 수정 금지</t>
-  </si>
-  <si>
-    <t>✅ 새 아이템 추가는 자유롭게 가능</t>
-  </si>
-  <si>
-    <t>✅ 교환/판매 O↔X, 판매보상 수치는 자유롭게 수정 가능</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -693,6 +726,20 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -712,7 +759,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -735,11 +782,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -765,6 +855,45 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1068,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1516,59 +1645,59 @@
       <c r="I15" s="10"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="13">
         <v>20</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="6" t="s">
+      <c r="F16" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="H16" s="13"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="18">
         <v>1</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="4">
+      <c r="F17" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="18">
         <v>50</v>
       </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="4"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -1598,61 +1727,61 @@
       <c r="I18" s="10"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="22">
         <v>3</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="4">
+      <c r="F19" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="22">
         <v>150</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="I19" s="24"/>
+      <c r="J19" s="22"/>
+    </row>
+    <row r="20" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="18">
         <v>1</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="4">
+      <c r="F20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="18">
         <v>20</v>
       </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="4"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
@@ -1682,81 +1811,81 @@
       <c r="I21" s="10"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="22">
         <v>1</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="4">
+      <c r="F22" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="22">
         <v>80</v>
       </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="I22" s="24"/>
+      <c r="J22" s="22"/>
+    </row>
+    <row r="23" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="18">
         <v>1</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="4">
-        <v>500</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J23" s="4">
-        <v>5</v>
+      <c r="G23" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="18">
+        <v>10</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="J23" s="18">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>62</v>
@@ -1765,30 +1894,30 @@
         <v>24</v>
       </c>
       <c r="H24" s="4">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="J24" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D25" s="4">
         <v>1</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>62</v>
@@ -1797,10 +1926,10 @@
         <v>24</v>
       </c>
       <c r="H25" s="4">
-        <v>700</v>
+        <v>10</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="J25" s="4">
         <v>5</v>
@@ -1808,19 +1937,19 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>24</v>
@@ -1831,24 +1960,28 @@
       <c r="H26" s="4">
         <v>10</v>
       </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="4"/>
+      <c r="I26" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="J26" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>24</v>
@@ -1859,24 +1992,28 @@
       <c r="H27" s="4">
         <v>10</v>
       </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="4"/>
+      <c r="I27" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="J27" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D28" s="4">
         <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>24</v>
@@ -1887,24 +2024,28 @@
       <c r="H28" s="4">
         <v>10</v>
       </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="4"/>
+      <c r="I28" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="J28" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D29" s="4">
         <v>1</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>24</v>
@@ -1915,124 +2056,128 @@
       <c r="H29" s="4">
         <v>10</v>
       </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="I29" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="J29" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="4">
+      <c r="C30" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="22">
         <v>1</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="4">
+      <c r="G30" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="22">
         <v>500</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="22">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="18">
         <v>1</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="4">
+      <c r="F31" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="18">
         <v>10</v>
       </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="I31" s="20"/>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="22">
         <v>2</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="4">
+      <c r="F32" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="22">
         <v>10</v>
       </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="4"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="I32" s="24"/>
+      <c r="J32" s="22"/>
+    </row>
+    <row r="33" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="18">
         <v>300</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="10" t="s">
+      <c r="F33" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="18"/>
+      <c r="I33" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J33" s="4">
+      <c r="J33" s="18">
         <v>1</v>
       </c>
     </row>
@@ -2098,10 +2243,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>117</v>
@@ -2110,7 +2255,7 @@
         <v>1000</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>24</v>
@@ -2128,10 +2273,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>117</v>
@@ -2140,7 +2285,7 @@
         <v>2000</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>24</v>
@@ -2156,77 +2301,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" s="22">
+        <v>3000</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="22"/>
+      <c r="I38" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="J38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C39" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D39" s="18">
+        <v>1</v>
+      </c>
+      <c r="E39" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="D38" s="4">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F38" s="6" t="s">
+      <c r="F39" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="4">
+      <c r="G39" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="18">
         <v>10</v>
       </c>
-      <c r="I38" s="10"/>
-      <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" s="4">
-        <v>1</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" s="4">
-        <v>10</v>
-      </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="4"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="18"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D40" s="4">
         <v>1</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>62</v>
@@ -2242,19 +2389,19 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D41" s="4">
         <v>1</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>62</v>
@@ -2268,73 +2415,75 @@
       <c r="I41" s="10"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+    <row r="42" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="22">
+        <v>1</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="22">
+        <v>10</v>
+      </c>
+      <c r="I42" s="24"/>
+      <c r="J42" s="22"/>
+    </row>
+    <row r="43" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C43" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D43" s="18">
+        <v>20</v>
+      </c>
+      <c r="E43" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="4">
-        <v>20</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="F43" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D43" s="4">
-        <v>10</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H43" s="4"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="4"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="18"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D44" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>24</v>
@@ -2346,66 +2495,92 @@
       <c r="I44" s="10"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" s="22">
+        <v>5</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="H45" s="22"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="22"/>
+    </row>
+    <row r="46" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B46" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C46" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D46" s="20">
+        <v>1</v>
+      </c>
+      <c r="E46" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="10">
+      <c r="F46" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="20">
+        <v>10</v>
+      </c>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" s="24">
         <v>1</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H45" s="10">
+      <c r="E47" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F47" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="24">
         <v>10</v>
       </c>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D46" s="10">
-        <v>1</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H46" s="10">
-        <v>10</v>
-      </c>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
+    </row>
+    <row r="48" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -2425,99 +2600,99 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -2525,15 +2700,15 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2541,32 +2716,32 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/items.xlsx
+++ b/items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9637BB9-E4E1-44F4-9431-675B1FD579FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D054A77-B9B0-46F7-BB48-BA561525DC43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="아이템" sheetId="1" r:id="rId1"/>
@@ -1964,7 +1964,7 @@
         <v>195</v>
       </c>
       <c r="J26" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -1996,7 +1996,7 @@
         <v>195</v>
       </c>
       <c r="J27" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -2028,7 +2028,7 @@
         <v>195</v>
       </c>
       <c r="J28" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -2060,7 +2060,7 @@
         <v>198</v>
       </c>
       <c r="J29" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">

--- a/items.xlsx
+++ b/items.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D054A77-B9B0-46F7-BB48-BA561525DC43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EB3A69-707E-462D-95DA-002E6C1C5A11}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,6 +308,18 @@
     <t>사용 시 샤르체류 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
   </si>
   <si>
+    <t>배진3강화제</t>
+  </si>
+  <si>
+    <t>천상펫알</t>
+  </si>
+  <si>
+    <t>🥚 천상펫알</t>
+  </si>
+  <si>
+    <t>사용 시 고오다,아마란 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
+  </si>
+  <si>
     <t>오형제(진화)알</t>
   </si>
   <si>
@@ -317,40 +329,34 @@
     <t>사용 시 오형제 진화 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
   </si>
   <si>
-    <t>천상펫알</t>
-  </si>
-  <si>
-    <t>🥚 천상펫알</t>
-  </si>
-  <si>
-    <t>사용 시 고오다,아마란 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
+    <t>카오닉스알</t>
+  </si>
+  <si>
+    <t>pet_egg</t>
+  </si>
+  <si>
+    <t>사용 시 카오닉스SD 교체 (환수 보정 유지)</t>
+  </si>
+  <si>
+    <t>언딘알</t>
+  </si>
+  <si>
+    <t>사용 시 언딘 교체 (환수 보정 유지)</t>
+  </si>
+  <si>
+    <t>공룡알</t>
+  </si>
+  <si>
+    <t>사용 시 공룡4종 1마리 랜덤 교체 (환수 보정 유지)</t>
   </si>
   <si>
     <t>쿵야알</t>
   </si>
   <si>
-    <t>pet_egg</t>
-  </si>
-  <si>
     <t>사용 시 쿵야펫 중 1마리로 교체 (환수 보정 유지)</t>
   </si>
   <si>
-    <t>카오닉스알</t>
-  </si>
-  <si>
-    <t>사용 시 카오닉스SD 교체 (환수 보정 유지)</t>
-  </si>
-  <si>
-    <t>언딘알</t>
-  </si>
-  <si>
-    <t>사용 시 언딘 교체 (환수 보정 유지)</t>
-  </si>
-  <si>
-    <t>공룡알</t>
-  </si>
-  <si>
-    <t>사용 시 공룡4종 1마리 랜덤 교체 (환수 보정 유지)</t>
+    <t>각성제</t>
   </si>
   <si>
     <t>운영진</t>
@@ -407,6 +413,9 @@
     <t>펫 경험치 +700</t>
   </si>
   <si>
+    <t>펫경문_1000</t>
+  </si>
+  <si>
     <t>📜 펫 경험의 문서 (+1000)</t>
   </si>
   <si>
@@ -422,6 +431,12 @@
     <t>펫 경험치 +2000</t>
   </si>
   <si>
+    <t>펫경문_3000</t>
+  </si>
+  <si>
+    <t>📜 펫 경험의 문서 (+3000)</t>
+  </si>
+  <si>
     <t>사냥상자_하급</t>
   </si>
   <si>
@@ -497,9 +512,6 @@
     <t>사용 시 지정초기화구슬 5개 획득</t>
   </si>
   <si>
-    <t>각성제</t>
-  </si>
-  <si>
     <t>💊 각성제</t>
   </si>
   <si>
@@ -509,15 +521,15 @@
     <t>버프,서포터펫에사용 한계치강화</t>
   </si>
   <si>
-    <t>☠️ 배진3 강화제</t>
+    <t>배진강화제</t>
+  </si>
+  <si>
+    <t>☠️ 배진강화제</t>
   </si>
   <si>
     <t>awakening_cc3</t>
   </si>
   <si>
-    <t>딜러펫 배진3 5%확률로 업그레이드</t>
-  </si>
-  <si>
     <t>[아이템 엑셀 사용법]</t>
   </si>
   <si>
@@ -614,42 +626,7 @@
     <t>✅ 교환/판매 O↔X, 판매보상 수치는 자유롭게 수정 가능</t>
   </si>
   <si>
-    <t>펫경문_1000</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>배진3강화제</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>펫경문_3000</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 펫 경험의 문서 (+3000)</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>각성제</t>
+    <t>딜러펫 배진 7%확률로 단계 업그레이드</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -657,7 +634,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -725,20 +702,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI Emoji"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1645,7 +1608,7 @@
       <c r="I15" s="10"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>66</v>
       </c>
@@ -1671,7 +1634,7 @@
       <c r="I16" s="16"/>
       <c r="J16" s="13"/>
     </row>
-    <row r="17" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
         <v>69</v>
       </c>
@@ -1727,7 +1690,7 @@
       <c r="I18" s="10"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
         <v>76</v>
       </c>
@@ -1755,7 +1718,7 @@
       <c r="I19" s="24"/>
       <c r="J19" s="22"/>
     </row>
-    <row r="20" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>28</v>
       </c>
@@ -1811,7 +1774,7 @@
       <c r="I21" s="10"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
         <v>85</v>
       </c>
@@ -1839,7 +1802,7 @@
       <c r="I22" s="24"/>
       <c r="J22" s="22"/>
     </row>
-    <row r="23" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
         <v>89</v>
       </c>
@@ -1865,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="I23" s="20" t="s">
-        <v>195</v>
+        <v>92</v>
       </c>
       <c r="J23" s="18">
         <v>10</v>
@@ -1873,10 +1836,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>90</v>
@@ -1885,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>62</v>
@@ -1897,7 +1860,7 @@
         <v>10</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>195</v>
+        <v>92</v>
       </c>
       <c r="J24" s="4">
         <v>7</v>
@@ -1905,10 +1868,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>90</v>
@@ -1917,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>62</v>
@@ -1929,7 +1892,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>195</v>
+        <v>92</v>
       </c>
       <c r="J25" s="4">
         <v>5</v>
@@ -1937,19 +1900,19 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>24</v>
@@ -1961,7 +1924,7 @@
         <v>10</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>195</v>
+        <v>92</v>
       </c>
       <c r="J26" s="4">
         <v>1</v>
@@ -1969,19 +1932,19 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>24</v>
@@ -1993,7 +1956,7 @@
         <v>10</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>195</v>
+        <v>92</v>
       </c>
       <c r="J27" s="4">
         <v>1</v>
@@ -2001,19 +1964,19 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D28" s="4">
         <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>24</v>
@@ -2025,7 +1988,7 @@
         <v>10</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>195</v>
+        <v>92</v>
       </c>
       <c r="J28" s="4">
         <v>1</v>
@@ -2033,19 +1996,19 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D29" s="4">
         <v>1</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>24</v>
@@ -2057,27 +2020,27 @@
         <v>10</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="J29" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D30" s="22">
         <v>1</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F30" s="26" t="s">
         <v>62</v>
@@ -2095,21 +2058,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D31" s="18">
         <v>1</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>24</v>
@@ -2123,21 +2086,21 @@
       <c r="I31" s="20"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>112</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>110</v>
       </c>
       <c r="D32" s="22">
         <v>2</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F32" s="23" t="s">
         <v>24</v>
@@ -2151,21 +2114,21 @@
       <c r="I32" s="24"/>
       <c r="J32" s="22"/>
     </row>
-    <row r="33" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D33" s="18">
         <v>300</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F33" s="19" t="s">
         <v>24</v>
@@ -2183,19 +2146,19 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="D34" s="4">
         <v>500</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>24</v>
@@ -2213,19 +2176,19 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D35" s="4">
         <v>700</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>24</v>
@@ -2243,19 +2206,19 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>194</v>
+        <v>127</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D36" s="4">
         <v>1000</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>24</v>
@@ -2273,19 +2236,19 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D37" s="4">
         <v>2000</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>24</v>
@@ -2301,21 +2264,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="21" t="s">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>197</v>
+        <v>134</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D38" s="22">
         <v>3000</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F38" s="23" t="s">
         <v>24</v>
@@ -2331,21 +2294,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A39" s="17" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D39" s="18">
         <v>1</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F39" s="25" t="s">
         <v>62</v>
@@ -2361,19 +2324,19 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D40" s="4">
         <v>1</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>62</v>
@@ -2389,19 +2352,19 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D41" s="4">
         <v>1</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>62</v>
@@ -2415,21 +2378,21 @@
       <c r="I41" s="10"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="21" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D42" s="22">
         <v>1</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F42" s="26" t="s">
         <v>62</v>
@@ -2443,21 +2406,21 @@
       <c r="I42" s="24"/>
       <c r="J42" s="22"/>
     </row>
-    <row r="43" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D43" s="18">
         <v>20</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F43" s="19" t="s">
         <v>24</v>
@@ -2471,19 +2434,19 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D44" s="4">
         <v>10</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>24</v>
@@ -2495,21 +2458,21 @@
       <c r="I44" s="10"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="21" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D45" s="22">
         <v>5</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F45" s="23" t="s">
         <v>24</v>
@@ -2521,21 +2484,21 @@
       <c r="I45" s="24"/>
       <c r="J45" s="22"/>
     </row>
-    <row r="46" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A46" s="17" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D46" s="20">
         <v>1</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F46" s="19" t="s">
         <v>24</v>
@@ -2549,21 +2512,21 @@
       <c r="I46" s="20"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="21" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D47" s="24">
         <v>1</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="F47" s="23" t="s">
         <v>24</v>
@@ -2577,7 +2540,7 @@
       <c r="I47" s="24"/>
       <c r="J47" s="24"/>
     </row>
-    <row r="48" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11"/>
@@ -2600,99 +2563,99 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -2700,15 +2663,15 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2716,32 +2679,32 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/items.xlsx
+++ b/items.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EB3A69-707E-462D-95DA-002E6C1C5A11}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB745D-CA81-400B-8D89-C2290872B1ED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="207">
   <si>
     <t>키
 (코드에서 사용)</t>
@@ -627,6 +627,32 @@
   </si>
   <si>
     <t>딜러펫 배진 7%확률로 단계 업그레이드</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>배진꾸러미</t>
+  </si>
+  <si>
+    <t>☠️ 배진꾸러미</t>
+  </si>
+  <si>
+    <t>bundle_cc_enhancer</t>
+  </si>
+  <si>
+    <t>각성제꾸러미</t>
+  </si>
+  <si>
+    <t>💊 각성제꾸러미</t>
+  </si>
+  <si>
+    <t>bundle_awakening</t>
+  </si>
+  <si>
+    <t>사용 시 배진강화제 50개 획득</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용 시 각성제 30개 획득</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -816,9 +842,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -857,6 +880,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1160,7 +1186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1609,58 +1635,58 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <v>20</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="15" t="s">
+      <c r="F16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="13"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="18">
-        <v>1</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="D17" s="17">
+        <v>1</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="18">
+      <c r="F17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="17">
         <v>50</v>
       </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="18"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="17"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -1691,60 +1717,60 @@
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>3</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="22">
+      <c r="F19" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="21">
         <v>150</v>
       </c>
-      <c r="I19" s="24"/>
-      <c r="J19" s="22"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="18">
-        <v>1</v>
-      </c>
-      <c r="E20" s="17" t="s">
+      <c r="D20" s="17">
+        <v>1</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="18">
+      <c r="F20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="17">
         <v>20</v>
       </c>
-      <c r="I20" s="20"/>
-      <c r="J20" s="18"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
@@ -1775,62 +1801,62 @@
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="22">
-        <v>1</v>
-      </c>
-      <c r="E22" s="21" t="s">
+      <c r="D22" s="21">
+        <v>1</v>
+      </c>
+      <c r="E22" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="22">
+      <c r="F22" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="21">
         <v>80</v>
       </c>
-      <c r="I22" s="24"/>
-      <c r="J22" s="22"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="18">
-        <v>1</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="D23" s="17">
+        <v>1</v>
+      </c>
+      <c r="E23" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="G23" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="18">
+      <c r="G23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="17">
         <v>10</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="17">
         <v>10</v>
       </c>
     </row>
@@ -2027,120 +2053,120 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="22">
-        <v>1</v>
-      </c>
-      <c r="E30" s="21" t="s">
+      <c r="D30" s="21">
+        <v>1</v>
+      </c>
+      <c r="E30" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="G30" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="22">
+      <c r="G30" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="21">
         <v>500</v>
       </c>
-      <c r="I30" s="24" t="s">
+      <c r="I30" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="18">
-        <v>1</v>
-      </c>
-      <c r="E31" s="17" t="s">
+      <c r="D31" s="17">
+        <v>1</v>
+      </c>
+      <c r="E31" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="F31" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="18">
+      <c r="F31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="17">
         <v>10</v>
       </c>
-      <c r="I31" s="20"/>
-      <c r="J31" s="18"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="17"/>
     </row>
     <row r="32" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>2</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="F32" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="22">
+      <c r="F32" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="21">
         <v>10</v>
       </c>
-      <c r="I32" s="24"/>
-      <c r="J32" s="22"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="21"/>
     </row>
     <row r="33" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="17">
         <v>300</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="F33" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="18"/>
-      <c r="I33" s="20" t="s">
+      <c r="F33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="J33" s="18">
+      <c r="J33" s="17">
         <v>1</v>
       </c>
     </row>
@@ -2265,62 +2291,62 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>3000</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="F38" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="22"/>
-      <c r="I38" s="24" t="s">
+      <c r="F38" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="21"/>
+      <c r="I38" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="18">
-        <v>1</v>
-      </c>
-      <c r="E39" s="17" t="s">
+      <c r="D39" s="17">
+        <v>1</v>
+      </c>
+      <c r="E39" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="G39" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" s="18">
+      <c r="G39" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="17">
         <v>10</v>
       </c>
-      <c r="I39" s="20"/>
-      <c r="J39" s="18"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="17"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
@@ -2379,58 +2405,58 @@
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="D42" s="22">
-        <v>1</v>
-      </c>
-      <c r="E42" s="21" t="s">
+      <c r="D42" s="21">
+        <v>1</v>
+      </c>
+      <c r="E42" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="F42" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="G42" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H42" s="22">
+      <c r="G42" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="21">
         <v>10</v>
       </c>
-      <c r="I42" s="24"/>
-      <c r="J42" s="22"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="21"/>
     </row>
     <row r="43" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="17">
         <v>20</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F43" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="25" t="s">
+      <c r="F43" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="H43" s="18"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="18"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="17"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
@@ -2459,92 +2485,148 @@
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C45" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="21">
         <v>5</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="F45" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" s="26" t="s">
+      <c r="F45" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="H45" s="22"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="22"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="21"/>
     </row>
     <row r="46" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D46" s="20">
-        <v>1</v>
-      </c>
-      <c r="E46" s="17" t="s">
+      <c r="D46" s="19">
+        <v>1</v>
+      </c>
+      <c r="E46" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="F46" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H46" s="20">
-        <v>10</v>
-      </c>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-    </row>
-    <row r="47" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="21" t="s">
+      <c r="F46" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="19"/>
+      <c r="I46" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="J46" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C47" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D47" s="24">
-        <v>1</v>
-      </c>
-      <c r="E47" s="21" t="s">
+      <c r="D47" s="10">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="F47" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H47" s="24">
-        <v>10</v>
-      </c>
-      <c r="I47" s="24"/>
-      <c r="J47" s="24"/>
-    </row>
-    <row r="48" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-    </row>
+      <c r="F47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="10"/>
+      <c r="I47" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J47" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D48" s="10">
+        <v>50</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="10">
+        <v>100</v>
+      </c>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+    </row>
+    <row r="49" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="D49" s="23">
+        <v>30</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="26">
+        <v>100</v>
+      </c>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+    </row>
+    <row r="50" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/items.xlsx
+++ b/items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB745D-CA81-400B-8D89-C2290872B1ED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6522F073-664E-4000-9E10-CB681B44F2A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="207">
   <si>
     <t>키
 (코드에서 사용)</t>
@@ -648,11 +648,11 @@
     <t>bundle_awakening</t>
   </si>
   <si>
-    <t>사용 시 배진강화제 50개 획득</t>
+    <t>사용 시 배진강화제 10개 획득</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>사용 시 각성제 30개 획득</t>
+    <t>사용 시 각성제 10개 획득</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -818,7 +818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -884,6 +884,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2536,7 +2538,7 @@
       <c r="I46" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="J46" s="19">
+      <c r="J46" s="27">
         <v>1</v>
       </c>
     </row>
@@ -2566,7 +2568,7 @@
       <c r="I47" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J47" s="10">
+      <c r="J47" s="28">
         <v>1</v>
       </c>
     </row>
@@ -2581,7 +2583,7 @@
         <v>201</v>
       </c>
       <c r="D48" s="10">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>205</v>
@@ -2592,11 +2594,13 @@
       <c r="G48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H48" s="10">
-        <v>100</v>
-      </c>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J48" s="28">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="20" t="s">
@@ -2609,7 +2613,7 @@
         <v>204</v>
       </c>
       <c r="D49" s="23">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E49" s="20" t="s">
         <v>206</v>
@@ -2620,11 +2624,13 @@
       <c r="G49" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H49" s="26">
-        <v>100</v>
-      </c>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J49" s="28">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>

--- a/items.xlsx
+++ b/items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6522F073-664E-4000-9E10-CB681B44F2A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A111C1-5C0B-4A58-9F29-22AC34FF245C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="209">
   <si>
     <t>키
 (코드에서 사용)</t>
@@ -653,6 +653,14 @@
   </si>
   <si>
     <t>사용 시 각성제 10개 획득</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>신수알</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용 시 신수 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -818,7 +826,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -886,6 +894,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1188,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1928,22 +1937,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>24</v>
+        <v>208</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>24</v>
@@ -1960,10 +1969,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>100</v>
@@ -1972,7 +1981,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>24</v>
@@ -1992,10 +2001,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>100</v>
@@ -2004,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>24</v>
@@ -2024,10 +2033,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>100</v>
@@ -2036,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>24</v>
@@ -2048,175 +2057,177 @@
         <v>10</v>
       </c>
       <c r="I29" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="J29" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="4">
+        <v>10</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J29" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="20" t="s">
+      <c r="J30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B31" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C31" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="21">
-        <v>1</v>
-      </c>
-      <c r="E30" s="20" t="s">
+      <c r="D31" s="21">
+        <v>1</v>
+      </c>
+      <c r="E31" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="F31" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="G30" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="21">
+      <c r="G31" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="21">
         <v>500</v>
       </c>
-      <c r="I30" s="23" t="s">
+      <c r="I31" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="J30" s="21">
+      <c r="J31" s="21">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="16" t="s">
+    <row r="32" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B32" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C32" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="17">
-        <v>1</v>
-      </c>
-      <c r="E31" s="16" t="s">
+      <c r="D32" s="17">
+        <v>1</v>
+      </c>
+      <c r="E32" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="F31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="17">
+      <c r="F32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="17">
         <v>10</v>
       </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="17"/>
-    </row>
-    <row r="32" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="20" t="s">
+      <c r="I32" s="19"/>
+      <c r="J32" s="17"/>
+    </row>
+    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D33" s="21">
         <v>2</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E33" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="F32" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="21">
+      <c r="F33" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="21">
         <v>10</v>
       </c>
-      <c r="I32" s="23"/>
-      <c r="J32" s="21"/>
-    </row>
-    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="16" t="s">
+      <c r="I33" s="23"/>
+      <c r="J33" s="21"/>
+    </row>
+    <row r="34" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B34" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C34" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D34" s="17">
         <v>300</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E34" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="F33" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="17"/>
-      <c r="I33" s="19" t="s">
+      <c r="F34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="17"/>
+      <c r="I34" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="J33" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="4">
-        <v>500</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J34" s="4">
-        <v>2</v>
+      <c r="J34" s="17">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>119</v>
       </c>
       <c r="D35" s="4">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>24</v>
@@ -2229,24 +2240,24 @@
         <v>28</v>
       </c>
       <c r="J35" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>119</v>
       </c>
       <c r="D36" s="4">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>24</v>
@@ -2256,27 +2267,27 @@
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="10" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J36" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>119</v>
       </c>
       <c r="D37" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>24</v>
@@ -2286,107 +2297,109 @@
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J37" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J37" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="20" t="s">
+      <c r="J38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B39" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C39" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="21">
+      <c r="D39" s="21">
         <v>3000</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E39" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="F38" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="21"/>
-      <c r="I38" s="23" t="s">
+      <c r="F39" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="21"/>
+      <c r="I39" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="J38" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="16" t="s">
+      <c r="J39" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B40" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C40" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="17">
-        <v>1</v>
-      </c>
-      <c r="E39" s="16" t="s">
+      <c r="D40" s="17">
+        <v>1</v>
+      </c>
+      <c r="E40" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F40" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="G39" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" s="17">
+      <c r="G40" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="17">
         <v>10</v>
       </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="17"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D40" s="4">
-        <v>1</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="4">
-        <v>10</v>
-      </c>
-      <c r="I40" s="10"/>
-      <c r="J40" s="4"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="17"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D41" s="4">
         <v>1</v>
@@ -2406,187 +2419,185 @@
       <c r="I41" s="10"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="20" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="4">
+        <v>10</v>
+      </c>
+      <c r="I42" s="10"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B43" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C43" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="D42" s="21">
-        <v>1</v>
-      </c>
-      <c r="E42" s="20" t="s">
+      <c r="D43" s="21">
+        <v>1</v>
+      </c>
+      <c r="E43" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F42" s="25" t="s">
+      <c r="F43" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="G42" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H42" s="21">
+      <c r="G43" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="21">
         <v>10</v>
       </c>
-      <c r="I42" s="23"/>
-      <c r="J42" s="21"/>
-    </row>
-    <row r="43" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="16" t="s">
+      <c r="I43" s="23"/>
+      <c r="J43" s="21"/>
+    </row>
+    <row r="44" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B44" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C44" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D44" s="17">
         <v>20</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E44" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F43" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="24" t="s">
+      <c r="F44" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="H43" s="17"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="17"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="H44" s="17"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="17"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B45" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D45" s="4">
         <v>10</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="F45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H44" s="4"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="20" t="s">
+      <c r="H45" s="4"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="B46" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C46" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D46" s="21">
         <v>5</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E46" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="F45" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" s="25" t="s">
+      <c r="F46" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="H45" s="21"/>
-      <c r="I45" s="23"/>
-      <c r="J45" s="21"/>
-    </row>
-    <row r="46" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="16" t="s">
+      <c r="H46" s="21"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="21"/>
+    </row>
+    <row r="47" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B47" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C47" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D46" s="19">
-        <v>1</v>
-      </c>
-      <c r="E46" s="16" t="s">
+      <c r="D47" s="19">
+        <v>1</v>
+      </c>
+      <c r="E47" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="F46" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H46" s="19"/>
-      <c r="I46" s="16" t="s">
+      <c r="F47" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="19"/>
+      <c r="I47" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="J46" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D47" s="10">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J47" s="28">
+      <c r="J47" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="D48" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>24</v>
@@ -2596,43 +2607,73 @@
       </c>
       <c r="H48" s="10"/>
       <c r="I48" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J48" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D49" s="10">
+        <v>10</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="10"/>
+      <c r="I49" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="J48" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="20" t="s">
+      <c r="J49" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B50" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C50" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="D49" s="23">
+      <c r="D50" s="23">
         <v>10</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E50" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="F49" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" s="26"/>
-      <c r="I49" s="3" t="s">
+      <c r="F50" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="26"/>
+      <c r="I50" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="J49" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="J50" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/items.xlsx
+++ b/items.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A111C1-5C0B-4A58-9F29-22AC34FF245C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05214EAD-C85D-400B-9374-0D23C64B41EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="아이템" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="213">
   <si>
     <t>키
 (코드에서 사용)</t>
@@ -308,7 +308,16 @@
     <t>사용 시 샤르체류 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
   </si>
   <si>
-    <t>배진3강화제</t>
+    <t>배진강화제</t>
+  </si>
+  <si>
+    <t>행운초기화구슬</t>
+  </si>
+  <si>
+    <t>🍀 행운초기화구슬</t>
+  </si>
+  <si>
+    <t>pet_lucky_reset</t>
   </si>
   <si>
     <t>천상펫알</t>
@@ -329,6 +338,12 @@
     <t>사용 시 오형제 진화 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
   </si>
   <si>
+    <t>신수알</t>
+  </si>
+  <si>
+    <t>사용 시 신수 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
+  </si>
+  <si>
     <t>카오닉스알</t>
   </si>
   <si>
@@ -437,6 +452,9 @@
     <t>📜 펫 경험의 문서 (+3000)</t>
   </si>
   <si>
+    <t>펫 경험치 +3000</t>
+  </si>
+  <si>
     <t>사냥상자_하급</t>
   </si>
   <si>
@@ -521,15 +539,39 @@
     <t>버프,서포터펫에사용 한계치강화</t>
   </si>
   <si>
-    <t>배진강화제</t>
-  </si>
-  <si>
     <t>☠️ 배진강화제</t>
   </si>
   <si>
     <t>awakening_cc3</t>
   </si>
   <si>
+    <t>딜러펫 배진 7%확률로 단계 업그레이드</t>
+  </si>
+  <si>
+    <t>배진꾸러미</t>
+  </si>
+  <si>
+    <t>☠️ 배진꾸러미</t>
+  </si>
+  <si>
+    <t>bundle_cc_enhancer</t>
+  </si>
+  <si>
+    <t>사용 시 배진강화제 10개 획득</t>
+  </si>
+  <si>
+    <t>각성제꾸러미</t>
+  </si>
+  <si>
+    <t>💊 각성제꾸러미</t>
+  </si>
+  <si>
+    <t>bundle_awakening</t>
+  </si>
+  <si>
+    <t>사용 시 각성제 10개 획득</t>
+  </si>
+  <si>
     <t>[아이템 엑셀 사용법]</t>
   </si>
   <si>
@@ -626,41 +668,7 @@
     <t>✅ 교환/판매 O↔X, 판매보상 수치는 자유롭게 수정 가능</t>
   </si>
   <si>
-    <t>딜러펫 배진 7%확률로 단계 업그레이드</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>배진꾸러미</t>
-  </si>
-  <si>
-    <t>☠️ 배진꾸러미</t>
-  </si>
-  <si>
-    <t>bundle_cc_enhancer</t>
-  </si>
-  <si>
-    <t>각성제꾸러미</t>
-  </si>
-  <si>
-    <t>💊 각성제꾸러미</t>
-  </si>
-  <si>
-    <t>bundle_awakening</t>
-  </si>
-  <si>
-    <t>사용 시 배진강화제 10개 획득</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용 시 각성제 10개 획득</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>신수알</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용 시 신수 펫 중 1마리로 선택교체 (환수 보정 유지)</t>
+    <t>펫을 1렙으로 초기화 (환수 보정·S베이스 유지)</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -826,7 +834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -834,7 +842,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -863,7 +870,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -873,15 +879,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -889,12 +891,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1276,1404 +1284,1429 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="F3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3">
         <v>10</v>
       </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="4"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>40</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="10" t="s">
+      <c r="F4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>60</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="10" t="s">
+      <c r="F5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>100</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="10" t="s">
+      <c r="F6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>150</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="10" t="s">
+      <c r="F7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="10" t="s">
+      <c r="F8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>2</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="F9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="3">
         <v>10</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="4"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="F10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="3">
         <v>20</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="4"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>4</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="4">
+      <c r="F11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="3">
         <v>40</v>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="4"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>5</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="4">
+      <c r="F12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="3">
         <v>50</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="4"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>6</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="4">
+      <c r="F13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="3">
         <v>60</v>
       </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>5</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="F14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="4"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>10</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="4"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>20</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="14" t="s">
+      <c r="F16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="12"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="11"/>
     </row>
     <row r="17" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="17">
-        <v>1</v>
-      </c>
-      <c r="E17" s="16" t="s">
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="17">
+      <c r="F17" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="15">
         <v>50</v>
       </c>
-      <c r="I17" s="19"/>
-      <c r="J17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="15"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>2</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="4">
+      <c r="F18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="3">
         <v>100</v>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="4"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="18">
         <v>3</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="21">
+      <c r="F19" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="18">
         <v>150</v>
       </c>
-      <c r="I19" s="23"/>
-      <c r="J19" s="21"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="17">
-        <v>1</v>
-      </c>
-      <c r="E20" s="16" t="s">
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="17">
+      <c r="F20" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="15">
         <v>20</v>
       </c>
-      <c r="I20" s="19"/>
-      <c r="J20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="15"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="4">
+      <c r="F21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="3">
         <v>40</v>
       </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="4"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="21">
-        <v>1</v>
-      </c>
-      <c r="E22" s="20" t="s">
+      <c r="D22" s="18">
+        <v>1</v>
+      </c>
+      <c r="E22" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="21">
+      <c r="F22" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="18">
         <v>80</v>
       </c>
-      <c r="I22" s="23"/>
-      <c r="J22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="17">
-        <v>1</v>
-      </c>
-      <c r="E23" s="16" t="s">
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G23" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="17">
+      <c r="G23" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="15">
         <v>10</v>
       </c>
-      <c r="I23" s="19" t="s">
+      <c r="I23" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="15">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="27"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="27"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="6" t="s">
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="4">
+      <c r="G25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="3">
         <v>10</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I25" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J25" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="3" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F25" s="6" t="s">
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="4">
+      <c r="G26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="3">
         <v>10</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I26" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J26" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C26" s="3" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F26" s="6" t="s">
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="4">
+      <c r="G27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="3">
         <v>10</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I27" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="J26" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="4">
+      <c r="J27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="3">
         <v>10</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I28" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="J27" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" s="4">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="4">
+      <c r="J28" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="3">
         <v>10</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I29" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="J28" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="J29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="4">
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="3">
         <v>10</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I30" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="J29" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="4">
+      <c r="J30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="3">
         <v>10</v>
       </c>
-      <c r="I30" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="J30" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" s="21">
-        <v>1</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="25" t="s">
+      <c r="I31" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="18">
+        <v>1</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="21">
+      <c r="G32" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="18">
         <v>500</v>
       </c>
-      <c r="I31" s="23" t="s">
+      <c r="I32" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="J31" s="21">
+      <c r="J32" s="18">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" s="17">
-        <v>1</v>
-      </c>
-      <c r="E32" s="16" t="s">
+    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="15">
+        <v>10</v>
+      </c>
+      <c r="I33" s="17"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="18">
+        <v>2</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="18">
+        <v>10</v>
+      </c>
+      <c r="I34" s="22"/>
+      <c r="J34" s="18"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="15">
+        <v>300</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="15"/>
+      <c r="I35" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="J35" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="3">
+        <v>500</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J36" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="3">
+        <v>700</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="I39" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="18">
+        <v>3000</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="18"/>
+      <c r="I40" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J40" s="18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" s="15">
+        <v>1</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="15">
+        <v>10</v>
+      </c>
+      <c r="I41" s="17"/>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="3">
+        <v>10</v>
+      </c>
+      <c r="I42" s="9"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="3">
+        <v>1</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="3">
+        <v>10</v>
+      </c>
+      <c r="I43" s="9"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" s="18">
+        <v>1</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="18">
+        <v>10</v>
+      </c>
+      <c r="I44" s="22"/>
+      <c r="J44" s="18"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" s="15">
+        <v>20</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H45" s="15"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="15"/>
+    </row>
+    <row r="46" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" s="3">
+        <v>10</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="D47" s="18">
+        <v>5</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H47" s="18"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="18"/>
+    </row>
+    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="17">
+      <c r="B48" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="D48" s="17">
+        <v>1</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="17"/>
+      <c r="I48" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="J48" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" s="9">
+        <v>1</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="9"/>
+      <c r="I49" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="J49" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D50" s="9">
         <v>10</v>
       </c>
-      <c r="I32" s="19"/>
-      <c r="J32" s="17"/>
-    </row>
-    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" s="21">
-        <v>2</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="21">
+      <c r="E50" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="9"/>
+      <c r="I50" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="J50" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" s="22">
         <v>10</v>
       </c>
-      <c r="I33" s="23"/>
-      <c r="J33" s="21"/>
-    </row>
-    <row r="34" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="17">
-        <v>300</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="17"/>
-      <c r="I34" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J34" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D35" s="4">
-        <v>500</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J35" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D36" s="4">
-        <v>700</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J36" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D37" s="4">
-        <v>1000</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J37" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="4">
-        <v>2000</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="4"/>
-      <c r="I38" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="J38" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="21">
-        <v>3000</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" s="21"/>
-      <c r="I39" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="J39" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="17">
-        <v>1</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="F40" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="17">
-        <v>10</v>
-      </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="17"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D41" s="4">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" s="4">
-        <v>10</v>
-      </c>
-      <c r="I41" s="10"/>
-      <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D42" s="4">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H42" s="4">
-        <v>10</v>
-      </c>
-      <c r="I42" s="10"/>
-      <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="D43" s="21">
-        <v>1</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G43" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H43" s="21">
-        <v>10</v>
-      </c>
-      <c r="I43" s="23"/>
-      <c r="J43" s="21"/>
-    </row>
-    <row r="44" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="D44" s="17">
-        <v>20</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="F44" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="17"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D45" s="4">
-        <v>10</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H45" s="4"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D46" s="21">
-        <v>5</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="H46" s="21"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="21"/>
-    </row>
-    <row r="47" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="D47" s="19">
-        <v>1</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="F47" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H47" s="19"/>
-      <c r="I47" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="J47" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D48" s="10">
-        <v>1</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H48" s="10"/>
-      <c r="I48" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J48" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D49" s="10">
-        <v>10</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" s="10"/>
-      <c r="I49" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J49" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="D50" s="23">
-        <v>10</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H50" s="26"/>
-      <c r="I50" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="J50" s="29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="E51" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G51" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="22"/>
+      <c r="I51" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="J51" s="25">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2691,149 +2724,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>166</v>
+      <c r="A1" s="6" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>170</v>
+      <c r="A7" s="7" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>171</v>
+      <c r="A8" s="8" t="s">
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>173</v>
+      <c r="A9" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>175</v>
+      <c r="A10" s="8" t="s">
+        <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>177</v>
+      <c r="A11" s="8" t="s">
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>179</v>
+      <c r="A12" s="8" t="s">
+        <v>193</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>181</v>
+      <c r="A13" s="8" t="s">
+        <v>195</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>183</v>
+      <c r="A14" s="8" t="s">
+        <v>197</v>
       </c>
       <c r="B14" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>185</v>
+      <c r="A15" s="8" t="s">
+        <v>199</v>
       </c>
       <c r="B15" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>187</v>
+      <c r="A16" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="B16" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>190</v>
+      <c r="A18" s="8" t="s">
+        <v>204</v>
       </c>
       <c r="B18" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
+      <c r="A19" s="7"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/items.xlsx
+++ b/items.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\new_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05214EAD-C85D-400B-9374-0D23C64B41EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA8959E-73AE-480F-BC0C-A83D02C5D58B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="아이템" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="219">
   <si>
     <t>키
 (코드에서 사용)</t>
@@ -320,6 +320,9 @@
     <t>pet_lucky_reset</t>
   </si>
   <si>
+    <t>펫을 1렙으로 초기화 (환수 보정·S베이스 유지)</t>
+  </si>
+  <si>
     <t>천상펫알</t>
   </si>
   <si>
@@ -365,6 +368,12 @@
     <t>사용 시 공룡4종 1마리 랜덤 교체 (환수 보정 유지)</t>
   </si>
   <si>
+    <t>백피아알</t>
+  </si>
+  <si>
+    <t>사용시 백피아 획득</t>
+  </si>
+  <si>
     <t>쿵야알</t>
   </si>
   <si>
@@ -572,6 +581,18 @@
     <t>사용 시 각성제 10개 획득</t>
   </si>
   <si>
+    <t>행운초기화꾸러미</t>
+  </si>
+  <si>
+    <t>🍀 행운초기화꾸러미</t>
+  </si>
+  <si>
+    <t>bundle_lucky_reset_orb</t>
+  </si>
+  <si>
+    <t>사용 시 행운초기화구슬 5개 획득</t>
+  </si>
+  <si>
     <t>[아이템 엑셀 사용법]</t>
   </si>
   <si>
@@ -666,10 +687,6 @@
   </si>
   <si>
     <t>✅ 교환/판매 O↔X, 판매보상 수치는 자유롭게 수정 가능</t>
-  </si>
-  <si>
-    <t>펫을 1렙으로 초기화 (환수 보정·S베이스 유지)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -764,7 +781,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -830,11 +847,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -902,6 +964,45 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1205,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1893,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>24</v>
@@ -1907,10 +2008,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" s="24" t="s">
         <v>90</v>
@@ -1919,7 +2020,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>62</v>
@@ -1939,10 +2040,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C26" s="24" t="s">
         <v>90</v>
@@ -1951,7 +2052,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>62</v>
@@ -1971,10 +2072,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C27" s="24" t="s">
         <v>90</v>
@@ -1983,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>62</v>
@@ -2003,19 +2104,19 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>24</v>
@@ -2035,19 +2136,19 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D29" s="3">
         <v>1</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>24</v>
@@ -2067,19 +2168,19 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D30" s="3">
         <v>1</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>24</v>
@@ -2097,21 +2198,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D31" s="3">
         <v>1</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>24</v>
@@ -2123,158 +2224,160 @@
         <v>10</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="J31" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
+    <row r="32" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C32" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="18">
-        <v>1</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="21" t="s">
+      <c r="C32" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="3">
+        <v>10</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="18">
+        <v>1</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="G32" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="18">
+      <c r="G33" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="18">
         <v>500</v>
       </c>
-      <c r="I32" s="22" t="s">
+      <c r="I33" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="J32" s="18">
+      <c r="J33" s="18">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" s="15">
-        <v>1</v>
-      </c>
-      <c r="E33" s="23" t="s">
+    <row r="34" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="F33" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="15">
+      <c r="B34" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="15">
+        <v>1</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="15">
         <v>10</v>
       </c>
-      <c r="I33" s="17"/>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="B34" s="25" t="s">
+      <c r="I34" s="17"/>
+      <c r="J34" s="15"/>
+    </row>
+    <row r="35" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="D34" s="18">
+      <c r="D35" s="18">
         <v>2</v>
       </c>
-      <c r="E34" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="18">
+      <c r="E35" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="18">
         <v>10</v>
       </c>
-      <c r="I34" s="22"/>
-      <c r="J34" s="18"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="15">
+      <c r="I35" s="22"/>
+      <c r="J35" s="18"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="15">
         <v>300</v>
       </c>
-      <c r="E35" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="17" t="s">
+      <c r="E36" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="J35" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="3">
-        <v>500</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="J36" s="3">
-        <v>2</v>
+      <c r="J36" s="15">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -2285,10 +2388,10 @@
         <v>130</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D37" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E37" s="24" t="s">
         <v>131</v>
@@ -2304,7 +2407,7 @@
         <v>28</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -2315,10 +2418,10 @@
         <v>133</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D38" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>134</v>
@@ -2334,10 +2437,10 @@
         <v>28</v>
       </c>
       <c r="J38" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
         <v>135</v>
       </c>
@@ -2345,10 +2448,10 @@
         <v>136</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D39" s="3">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E39" s="24" t="s">
         <v>137</v>
@@ -2364,96 +2467,98 @@
         <v>28</v>
       </c>
       <c r="J39" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="C40" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" s="18">
-        <v>3000</v>
-      </c>
-      <c r="E40" s="25" t="s">
+      <c r="C40" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E40" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F40" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="18"/>
+      <c r="F40" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="3"/>
       <c r="I40" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J40" s="18">
+      <c r="J40" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="18">
+        <v>3000</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="18"/>
+      <c r="I41" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" s="18">
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="D41" s="15">
-        <v>1</v>
-      </c>
-      <c r="E41" s="23" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="B42" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="15">
+        <v>1</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="G41" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" s="15">
+      <c r="G42" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="15">
         <v>10</v>
       </c>
-      <c r="I41" s="17"/>
-      <c r="J41" s="15"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D42" s="3">
-        <v>1</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H42" s="3">
-        <v>10</v>
-      </c>
-      <c r="I42" s="9"/>
-      <c r="J42" s="3"/>
-    </row>
-    <row r="43" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I42" s="17"/>
+      <c r="J42" s="15"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="24" t="s">
         <v>148</v>
       </c>
@@ -2467,7 +2572,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>62</v>
@@ -2481,229 +2586,283 @@
       <c r="I43" s="9"/>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="25" t="s">
+    <row r="44" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="C44" s="25" t="s">
+      <c r="C44" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="D44" s="18">
-        <v>1</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="F44" s="21" t="s">
+      <c r="D44" s="3">
+        <v>1</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G44" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H44" s="18">
+      <c r="G44" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="3">
         <v>10</v>
       </c>
-      <c r="I44" s="22"/>
-      <c r="J44" s="18"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="23" t="s">
+      <c r="I44" s="9"/>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="18">
+        <v>1</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="18">
+        <v>10</v>
+      </c>
+      <c r="I45" s="22"/>
+      <c r="J45" s="18"/>
+    </row>
+    <row r="46" spans="1:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" s="29">
         <v>20</v>
       </c>
-      <c r="E45" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" s="20" t="s">
+      <c r="E46" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="F46" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="H45" s="15"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="15"/>
-    </row>
-    <row r="46" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" s="3">
+      <c r="H46" s="29"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="29"/>
+    </row>
+    <row r="47" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="D47" s="34">
         <v>10</v>
       </c>
-      <c r="E46" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="5" t="s">
+      <c r="E47" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="F47" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="3"/>
-    </row>
-    <row r="47" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="B47" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="D47" s="18">
+      <c r="H47" s="34"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="34"/>
+    </row>
+    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="B48" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D48" s="34">
         <v>5</v>
       </c>
-      <c r="E47" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" s="21" t="s">
+      <c r="E48" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="F48" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="H47" s="18"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="18"/>
-    </row>
-    <row r="48" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="B48" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="D48" s="17">
-        <v>1</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="F48" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H48" s="17"/>
-      <c r="I48" s="23" t="s">
+      <c r="H48" s="34"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="34"/>
+    </row>
+    <row r="49" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="B49" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="C49" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="D49" s="39">
+        <v>5</v>
+      </c>
+      <c r="E49" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="F49" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="H49" s="39"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="39"/>
+    </row>
+    <row r="50" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D50" s="17">
+        <v>1</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="17"/>
+      <c r="I50" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="J48" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="24" t="s">
+      <c r="J50" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="D49" s="9">
-        <v>1</v>
-      </c>
-      <c r="E49" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" s="9"/>
-      <c r="I49" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="J49" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="24" t="s">
+      <c r="B51" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="B50" s="24" t="s">
+      <c r="C51" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="D51" s="9">
+        <v>1</v>
+      </c>
+      <c r="E51" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="D50" s="9">
+      <c r="F51" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="9"/>
+      <c r="I51" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="J51" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="B52" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="9">
         <v>10</v>
       </c>
-      <c r="E50" s="24" t="s">
+      <c r="E52" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="9"/>
+      <c r="I52" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="J52" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="D53" s="22">
+        <v>10</v>
+      </c>
+      <c r="E53" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="22"/>
+      <c r="I53" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H50" s="9"/>
-      <c r="I50" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="J50" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="D51" s="22">
-        <v>10</v>
-      </c>
-      <c r="E51" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H51" s="22"/>
-      <c r="I51" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="J51" s="25">
+      <c r="J53" s="25">
         <v>1</v>
       </c>
     </row>
@@ -2725,99 +2884,99 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B11" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B14" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -2825,15 +2984,15 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2841,32 +3000,32 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
